--- a/data/xlsx/bkmea--production-planning-and-supply-chain-management.xlsx
+++ b/data/xlsx/bkmea--production-planning-and-supply-chain-management.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -714,7 +720,9 @@
       <c r="C19" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -736,7 +744,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -758,7 +768,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -780,7 +792,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -802,7 +816,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -824,7 +840,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -846,7 +864,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -868,7 +888,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>

--- a/data/xlsx/bkmea--production-planning-and-supply-chain-management.xlsx
+++ b/data/xlsx/bkmea--production-planning-and-supply-chain-management.xlsx
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
